--- a/artfynd/A 31447-2020 artfynd.xlsx
+++ b/artfynd/A 31447-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651753</v>
+        <v>119651757</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515188</v>
+        <v>515087</v>
       </c>
       <c r="R2" t="n">
-        <v>7136001</v>
+        <v>7135655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651757</v>
+        <v>119651753</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515087</v>
+        <v>515188</v>
       </c>
       <c r="R3" t="n">
-        <v>7135655</v>
+        <v>7136001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
